--- a/ct_scoop_links_2026-04-02.xlsx
+++ b/ct_scoop_links_2026-04-02.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,103 +440,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SOUTHINGTON SCOOP: Couch Potato opens in Southington</t>
+          <t>HARTFORD SCOOP: LuAnn's opens in Downtown Hartford, take a look inside</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/southington-scoop-couch-potato-opens-in-southington</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/hartford-scoop-luanns-opens-in-downtown-hartford-take-a-look-inside</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRESTON SCOOP: Lu-Mac's relocating to new building with Jimmies!</t>
+          <t>BROOKFIELD SCOOP: Birdcode sets opening date for Brookfield location!</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/preston-scoop-lu-macs-relocating-to-new-building-with-jimmies</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/brookfield-scoop-birdcode-sets-opening-date-for-brookfield-location</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EAST WINDSOR SCOOP: Molly's Sweet Spot coming soon!</t>
+          <t>NORWALK SCOOP: Ulta Beauty to open at Darinor Plaza</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-windsor-scoop-mollys-sweet-spot-coming-soon</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/norwalk-scoop-ulta-beauty-to-open-at-darinor-plaza</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOUTH WINDSOR SCOOP: New UConn Gampel Pavilion merchandise store opening!</t>
+          <t>OLD SAYBROOK SCOOP: Dock &amp; Dine landswap approved by voters</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-new-uconn-gampel-pavilion-merchandise-store-opening</t>
+          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/old-saybrook-scoop-dock-dine-landswap-approved-by-voters</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEW HAVEN SCOOP: 7 Brew sets opening date!</t>
+          <t>SOUTHINGTON SCOOP: Couch Potato opens in Southington</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/new-haven-scoop-7-brew-sets-opening-date</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/southington-scoop-couch-potato-opens-in-southington</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MILFORD SCOOP: Sprouts Farmers Market coming to Hooters site</t>
+          <t>PRESTON SCOOP: Lu-Mac's relocating to new building with Jimmies!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-sprouts-farmers-market-coming-to-hooters-site</t>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/preston-scoop-lu-macs-relocating-to-new-building-with-jimmies</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WEST SPRINGFIELD SCOOP: Ross Dress for Less eyeing former Big Lots for new location!</t>
+          <t>EAST WINDSOR SCOOP: Molly's Sweet Spot coming soon!</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-windsor-scoop-mollys-sweet-spot-coming-soon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SOUTH WINDSOR SCOOP: New UConn Gampel Pavilion merchandise store opening!</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-new-uconn-gampel-pavilion-merchandise-store-opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW HAVEN SCOOP: 7 Brew sets opening date!</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/new-haven-scoop-7-brew-sets-opening-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MILFORD SCOOP: Sprouts Farmers Market coming to Hooters site</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-sprouts-farmers-market-coming-to-hooters-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WEST SPRINGFIELD SCOOP: Ross Dress for Less eyeing former Big Lots for new location!</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-mass-posts/west-springfield-scoop-ross-dress-for-less-eyeing-former-big-lots-for-new-location</t>
         </is>
